--- a/docs/test-files/employee-register.xlsx
+++ b/docs/test-files/employee-register.xlsx
@@ -33,7 +33,7 @@
     <t>Jordan Hale</t>
   </si>
   <si>
-    <t>jordan.hale@northwind-synth.test</t>
+    <t>jordan.hale@northwind-industries.io</t>
   </si>
   <si>
     <t>123-45-6789</t>

--- a/docs/test-files/employee-register.xlsx
+++ b/docs/test-files/employee-register.xlsx
@@ -33,7 +33,7 @@
     <t>Jordan Hale</t>
   </si>
   <si>
-    <t>jordan.hale@northwind-industries.io</t>
+    <t>jordan.hale@securemind.chat</t>
   </si>
   <si>
     <t>123-45-6789</t>
